--- a/api/templates/device_activity/es.xlsx
+++ b/api/templates/device_activity/es.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\device_activity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A08E78C-13F8-47D0-9DDA-F74D0F38C43E}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26EE0E2-D445-4C5F-A259-CF15026A3614}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35571" yWindow="1329" windowWidth="22989" windowHeight="16080" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35570" yWindow="1330" windowWidth="22990" windowHeight="16080" tabRatio="815" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Activity" sheetId="1" r:id="rId1"/>
+    <sheet name="Activitidad resumen" sheetId="1" r:id="rId1"/>
+    <sheet name="Actividad por tipo de ensayo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029" fullPrecision="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
@@ -65,6 +66,15 @@
   </si>
   <si>
     <t>Última Carga</t>
+  </si>
+  <si>
+    <t>Device Activity by Assay</t>
+  </si>
+  <si>
+    <t>&lt;assayName&gt;</t>
+  </si>
+  <si>
+    <t>Ensayo</t>
   </si>
 </sst>
 </file>
@@ -584,56 +594,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="26.35546875" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" customWidth="1"/>
     <col min="4" max="4" width="29.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:5" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -650,7 +660,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>2</v>
       </c>
@@ -671,4 +681,119 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA49D63-7DD3-4887-BD34-0EDA075B9F0E}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="37.33203125" customWidth="1"/>
+    <col min="4" max="4" width="36.58203125" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/api/templates/device_activity/es.xlsx
+++ b/api/templates/device_activity/es.xlsx
@@ -1,32 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\device_activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54521E8A-EFC2-4E61-83CB-932F4B043706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Activitidad resumen" sheetId="1" r:id="rId1"/>
-    <sheet name="Actividad por tipo de ensayo" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Activitidad resumen" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Actividad por tipo de ensayo" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
   <si>
     <t>Actividad de dispositivos</t>
   </si>
@@ -46,6 +35,9 @@
     <t>Dispositivos</t>
   </si>
   <si>
+    <t>Sitio</t>
+  </si>
+  <si>
     <t>Nro. De serie</t>
   </si>
   <si>
@@ -61,6 +53,9 @@
     <t>&lt;name&gt;</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;serial&gt;</t>
   </si>
   <si>
@@ -82,41 +77,48 @@
     <t>Ensayo</t>
   </si>
   <si>
+    <t>Ultima Actualización de Resultados</t>
+  </si>
+  <si>
     <t>&lt;assayName&gt;</t>
-  </si>
-  <si>
-    <t>Ultima Actualización de Resultados</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d&quot;, &quot;yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm d&quot;, &quot;yyyy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
       <family val="2"/>
-      <charset val="1"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -142,18 +144,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
@@ -164,8 +158,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -174,74 +168,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -549,44 +475,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.796875" customWidth="1"/>
-    <col min="2" max="2" width="26.296875" customWidth="1"/>
-    <col min="3" max="3" width="18.19921875" customWidth="1"/>
-    <col min="4" max="4" width="29.5" customWidth="1"/>
-    <col min="5" max="5" width="18.796875" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="26.296875" customWidth="1"/>
+    <col min="4" max="4" width="18.19921875" customWidth="1"/>
+    <col min="5" max="5" width="29.5" customWidth="1"/>
+    <col min="6" max="6" width="18.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" ht="33" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -602,116 +529,134 @@
       <c r="E7" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
       <c r="D8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="8.59765625" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="38.796875" customWidth="1"/>
-    <col min="3" max="3" width="37.296875" customWidth="1"/>
-    <col min="4" max="4" width="36.59765625" customWidth="1"/>
-    <col min="5" max="5" width="19.296875" customWidth="1"/>
-    <col min="6" max="6" width="17.19921875" customWidth="1"/>
+    <col min="1" max="1" width="38.796875" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="38.796875" customWidth="1"/>
+    <col min="4" max="4" width="37.296875" customWidth="1"/>
+    <col min="5" max="5" width="36.59765625" customWidth="1"/>
+    <col min="6" max="6" width="19.296875" customWidth="1"/>
+    <col min="7" max="7" width="17.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" ht="21" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>12</v>
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
+        <v>15</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>